--- a/光伏配储项目/电价数据/2026/智合站.xlsx
+++ b/光伏配储项目/电价数据/2026/智合站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51062</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74374</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57012</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58261</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5062099999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50338</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45441</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11971</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09748999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10754</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09448000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11806</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10852</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14731</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.13857</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09031</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.11234</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.08284999999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15819</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21898</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.27667</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21919</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.11624</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.01054</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15665</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19391</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.59581</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.51144</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.0703</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40543</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6064299999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.43304</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57077</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6109</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.80363</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63861</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.62529</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.74987</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9524900000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66837</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6606000000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.72061</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.65698</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6566799999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63837</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6088300000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47073</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49555</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42611</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6944199999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80925</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.30198</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8868400000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52863</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51875</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50527</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50745</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48872</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49944</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59589</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7026</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42151</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51061</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17268</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.85321</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.04469</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.90986</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.50374</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.11676</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48499</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27037</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.48298</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5772</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.70875</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5521699999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68859</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7609900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7764800000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.57238</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5351399999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8696499999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.52234</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06479</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.63946</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33468</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.55745</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6031599999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.49107</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44321</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46057</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47384</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.46015</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.60665</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.46469</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.47443</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20459</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.66592</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50528</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.40211</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.48485</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.63576</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52923</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.61122</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.59075</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59387</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46633</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48745</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40686</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.47587</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34246</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.13166</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20696</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.18201</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5048899999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46994</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.08839</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07229000000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17386</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.18322</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.20689</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.55299</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.13574</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.21923</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23469</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24064</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20748</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26732</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13599</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5958600000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45667</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29793</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27904</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26005</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.06643</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04354</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.06603000000000001</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.07048</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04429</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04527</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05678</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04606</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03612</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04743</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04404</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04348</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04353</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04287</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04279</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04412</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04641</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04607</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21883</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05536</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.17384</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.07135999999999999</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.12586</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35092</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44603</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42318</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04346</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04690999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04384</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04391</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04404</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10295</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04317</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04536</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04512</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04515</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04597</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04458</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20016</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14299</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26913</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3357</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31798</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17255</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17113</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15878</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45558</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41822</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78103</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92041</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49457</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91643</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86949</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29993</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89415</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63279</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19364</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5457000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33754</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03752</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53746</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79662</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77866</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78204</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87747</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87683</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49845</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40386</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40678</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45603</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21388</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87914</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5512100000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62866</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54006</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45671</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45032</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5865900000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5960599999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6021299999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66508</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4694700000000001</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41818</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5805800000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8779</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63105</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.88589</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8680399999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44159</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35343</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92248</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47354</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27093</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16559</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26223</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19924</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19687</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25565</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44814</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8902</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.26101</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.07922</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6729700000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7544099999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.62261</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.55986</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43001</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38429</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.43968</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39337</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48245</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5791499999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25096</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.58282</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.5945900000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.57216</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.47893</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26205</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25702</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57443</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4541</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.72487</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.45294</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.324</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.5559400000000001</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.25001</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16516</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16943</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.49792</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.16074</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15651</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28033</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.17158</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.22414</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.13187</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10882</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17962</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15966</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16431</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43512</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43546</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34882</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.52216</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.45593</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26529</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19924</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24887</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24202</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24121</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24554</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3578</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.46629</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47866</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.48239</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.01988</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22506</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.55349</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71821</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28614</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34956</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.44944</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.73311</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.74766</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.50414</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45211</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35815</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14834</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25886</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28054</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21856</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26275</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14938</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43491</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.55275</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.7093700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.75937</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.49123</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.77604</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.57072</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.94104</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46946</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48245</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49116</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5926900000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.52854</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42666</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41149</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38307</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42084</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55901</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.48665</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4407799999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.62641</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.47925</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44247</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42687</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.53391</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.5013500000000001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6426499999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15813</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28522</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48218</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43225</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5698799999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6649400000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.86714</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.8822000000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.88063</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.69204</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80735</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.62426</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5871900000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.03239</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.94263</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63951</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.7468400000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47425</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.53243</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47751</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.51836</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.58089</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42896</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.48153</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.47636</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44089</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.48445</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.17827</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43909</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46326</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11075</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18043</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38772</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36534</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44454</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22717</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23045</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25006</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25392</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13986</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24928</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25101</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16965</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18141</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22874</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23334</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35009</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25501</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24175</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.1661</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20466</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01802</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03004</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10832</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01769</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03943</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01837</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04107</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0482</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04778</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02606</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02827</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.14318</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00255</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0341</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17184</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23488</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26492</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26282</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26866</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13343</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.56232</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.15641</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23521</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21843</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24445</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24542</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26778</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26901</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24876</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27593</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22532</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.15379</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.63058</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6225499999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.65036</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5704400000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.15888</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09508</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23624</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17502</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.12409</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.07736</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22713</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.10621</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.03045</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.04007</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.09645999999999999</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.17301</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02694</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.11524</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.14351</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01959</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.09823</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10682</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10726</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14058</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25584</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36498</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32344</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.009179999999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6071599999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.46039</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.49293</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14088</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.4981</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.44226</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33774</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.70326</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.66613</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26143</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5053799999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.3783</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.51003</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.7343</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.38395</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47937</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26993</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40484</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.41827</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.44367</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.60512</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5422899999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.60041</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.59265</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47738</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.37212</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.0231</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6668999999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.65112</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48532</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.38744</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.23361</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14499</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.24486</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16958</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06317</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.16788</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03183</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19963</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16405</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15773</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05696</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05335</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06869</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.15489</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07557999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05624000000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17074</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14567</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16486</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43717</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.7454400000000001</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38502</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06363</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42827</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25947</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.25823</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11309</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01728</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16641</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04090999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00527</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01864</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16543</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04568999999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23812</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.16032</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48749</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4065</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.60851</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.84711</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44251</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40886</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37396</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6633300000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14428</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20746</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23112</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23329</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15089</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02845</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.01338</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04699</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04624</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04669</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04509000000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04174</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07894</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02913</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09693</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17105</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19571</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12077</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22916</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12398</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04478</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11727</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23661</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.1864</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.2393</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20438</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24577</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54089</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.42243</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38107</v>
       </c>
     </row>
   </sheetData>
